--- a/results/job_matches_2026-09-14.xlsx
+++ b/results/job_matches_2026-09-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e66b988bfbe6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Cloud &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Farmers and Merchants Bank of Long Beach</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Seal Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+          <t>Developer DBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Bank of Long Beach</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,147 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1028ad7a9aa73a</t>
+          <t>https://www.indeed.com/viewjob?jk=84607e3a06c12fdd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Database Developer (SQL &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rooms To Go</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Seffner, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Databricks Lakehouse, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27110d8079f69f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Splunk, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b2625881e5f2a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc069827c03f863b</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer III-ETL/PySpark</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84607e3a06c12fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=7291666cf90be22a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-14.xlsx
+++ b/results/job_matches_2026-09-14.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineer</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,15 +478,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb83d271754206d</t>
+          <t>https://www.indeed.com/viewjob?jk=98c558c6b0a21fef</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Cloud &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Farmers and Merchants Bank of Long Beach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Seal Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d764d5c996e8a37</t>
+          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+          <t>Developer DBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Bank of Long Beach</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Developer DBA</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Nakupuna Companies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
+          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Database Developer (SQL &amp; Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rooms To Go</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seffner, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Databricks Lakehouse, SQL Server, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84607e3a06c12fdd</t>
+          <t>https://www.indeed.com/viewjob?jk=7291666cf90be22a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Database Developer (SQL &amp; Databricks)</t>
+          <t>Sr Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rooms To Go</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seffner, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Databricks Lakehouse, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291666cf90be22a</t>
+          <t>https://www.indeed.com/viewjob?jk=068d737aa1c3172d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-14.xlsx
+++ b/results/job_matches_2026-09-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks</t>
+          <t>AWS Python Data Engineer-6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c558c6b0a21fef</t>
+          <t>https://www.indeed.com/viewjob?jk=aa471a4093b491aa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Bank of Long Beach</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Developer DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,112 +566,742 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
+          <t>https://www.indeed.com/viewjob?jk=b69a57d634f44c20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nakupuna Companies</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Database Developer (SQL &amp; Databricks)</t>
+          <t>Senior Java Full Stack Developer-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rooms To Go</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seffner, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Databricks Lakehouse, SQL Server, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7291666cf90be22a</t>
+          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>BI / Data Architect (Remote)-6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Marlborough, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d7214291c7c2637</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Enterprise Cloud Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7202b7d449bfa36a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Global Payments</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Core specialty</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Life Sciences.AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>clickhouse</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Developer-Information Services Senior</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Indiana University Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Farmers and Merchants Bank of Long Beach</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Seal Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Platform Administrator (Databricks)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nitka Technologies</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Volantsoft Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01c19f449674df9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer (Full Stack Developer) - Remote</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Developer DBA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aeroflow Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nakupuna Companies</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Sr Cloud Security Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Adobe</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Lehi, UT, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D23" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=068d737aa1c3172d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GCP Data Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acfc93badebee67f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer, Core Systems</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>QuickNode</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hallandale Beach, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Datadog</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44dbc0a1e62ab6b6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-14.xlsx
+++ b/results/job_matches_2026-09-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Python Data Engineer-6</t>
+          <t>Software Engineer III - Databricks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa471a4093b491aa</t>
+          <t>https://www.indeed.com/viewjob?jk=98c558c6b0a21fef</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>AWS Python Data Engineer-6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa471a4093b491aa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Google Cloud Platform, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b69a57d634f44c20</t>
+          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. AI Data Engineer</t>
+          <t>Senior Engineer - Hyperscale Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Park Place Technologies</t>
+          <t>Veeam Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Highland Heights, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, HDFS, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
+          <t>https://www.indeed.com/viewjob?jk=f17632f11610e0ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer-1</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Solutions Architect</t>
+          <t>Senior Java Full Stack Developer-1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7202b7d449bfa36a</t>
+          <t>https://www.indeed.com/viewjob?jk=27628c1d7944c002</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
+          <t>https://www.indeed.com/viewjob?jk=7202b7d449bfa36a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Developer-Information Services Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Indiana University Health</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
+          <t>https://www.indeed.com/viewjob?jk=7398d2f9ab83a441</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Bank of Long Beach</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, GCP, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Administrator (Databricks)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nitka Technologies</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa44fdea0190b34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Quality Analyst</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Volantsoft Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c19f449674df9d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7312f22356e37b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer (Full Stack Developer) - Remote</t>
+          <t>Software Engineer III - PySpark/AWS/Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, PySpark, Scala, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
+          <t>https://www.indeed.com/viewjob?jk=12b2d3a25dd65381</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Developer-Information Services Senior</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Indiana University Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+          <t>https://www.indeed.com/viewjob?jk=afda63d4c955805b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8820ee81d8c77a67</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Developer DBA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb4b4b353eb8bc7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nakupuna Companies</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
+          <t>https://www.indeed.com/viewjob?jk=09c607a8a6e9e6e1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+          <t>https://www.indeed.com/viewjob?jk=00deb545cdf8539e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=068d737aa1c3172d</t>
+          <t>https://www.indeed.com/viewjob?jk=f436c35b9293c1bb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,5012 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfc93badebee67f</t>
+          <t>https://www.indeed.com/viewjob?jk=42fde78a8e52a847</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer, Core Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QuickNode</t>
+          <t>Hylant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hallandale Beach, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93f331567a1b25da</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ecdb7549167f466</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Independence, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0157f56a6e27cad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bloomington, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ced0409c76f4850</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f97eb4b6c78e57e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=080ed824e7309c6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e9941187a535d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Findlay, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26792be3f1ce7d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40097b188627fc8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=438fab27a54b95e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c6e53394ba3aa7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e32d13892fbf579</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c82bfdcacec2b79</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18104515e179e7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d522390ab1db0241</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad72ad30f1ab368</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Carolina, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be64c2d5635296ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f694fd137783bdde</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=299f65eca357474b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78155475e0b7db74</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fc3e569ad89e0eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=614cf434248f98f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2629ad6556cbacf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8218cb998a5c0151</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01de0a106d50019f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Carolina, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a08ea81549a22f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56c3823d88792143</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a55c291dace4b53</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b3cff0ccd0ca269</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fae7a2c2e6e1358</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=016a658dc9ac3489</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc0d0f1f18eb8438</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47971bbc08557e3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7bfcc94d4b3f34a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f49f733f65d11ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8330457e7c7d4248</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f90aa460666eb778</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6701998be316239a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d920562d203a185e</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aa55866530a52ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a565c5a09573c96</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Birmingham, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea61995aa36120f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885e1f5bffaa36a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Dublin, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77ba46a2cdbcf8ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0101e7a2a0fedfa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=570dfe76b557e2f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Elkhart, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d348ebc076adb84</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98d25fbfe90fcd1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13b85db8861d59de</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ffc3524695bd37a</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09d343f340846bb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Toledo, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86fe5a29c6f478bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a71a75a7a6f6ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4822d68866185d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e8c551e853470e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7b3b740adef358e</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hylant</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28bf28a64e288c3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Farmers and Merchants Bank of Long Beach</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Seal Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Platform Administrator (Databricks)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Nitka Technologies</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, IAM, Databricks, Unity Catalog, Hive, Spark, Kafka, Time Travel</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=414be1be9d96afd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Expert Analyst Data Management</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Fort Washington, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Terraform</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5149b914c1018629</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer III - ML Model Delivery</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, ECS, RDS, Databricks, Spark, Scala, MLOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fc384810dc1e31d</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeadc804a9484d0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a28368c599a0643</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=220fde5a7ab61250</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34b1402bf6437dcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Clinton, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f19c9e531ef55a20</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fargo, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9e73c822f8844a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85c7d84effba6226</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60c7d9e06cdaf076</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f12a1ca162239a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Liberty, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d94a40eeb0b40c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Newmarket, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6294f6e595512d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885e9edc1afd7aa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25e0a7f11b2f5765</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80a579dae67397ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5feacfc39b3d5f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Newport, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d8a52daee3e8452</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ed8e336465d87a</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25a3d0fe6ce79647</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Medway, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f686962a348d2f1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Watson, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Marion, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4581f1a3af15cc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hudson, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ed08d422e18d838</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3d42ed3ce6788ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Barrington, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54f7850a724e338c</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b45d9f24f862a12b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tyler, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=834a146cee4b0ee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Frankfort, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66bfe8bbf500669f</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b8778237b3a9a9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Honolulu, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f5dfcba34d7a802</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dayton, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32f10a5c826d77c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1964898c1fe8582</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5340ba338a6dbdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Parlin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04ad3829889eff15</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Derby, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee4a69c65915dae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb5879047bb49aa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=736a88fef080818b</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4914aa2faa0a7d7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09950965e6e09286</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc817f9191b34c97</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Caldwell, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19ab03de0b3dc4f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b7ac807f2bfd018</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Rehoboth Beach, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2998b67c6e643dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Stafford, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ee0e59c6632733f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Palmer, AK, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89b194674200ed2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1e7316082fa5dfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=706b0b9e31c343c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Dask, PostgreSQL, Git, Python</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf9c2207875eb310</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Cotulla Education</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=912b403391eebae1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a4124e344d24526</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, S3, Databricks, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ｃollective</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, RDS, GCP, BigQuery, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57341d2f2afa0500</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Smile Partners USA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42652418f10ddaf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Identity</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Zeta Global</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8127a1fdd36b3f92</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Identity</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Zeta Global</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ELT, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0c452b1635ef45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IT Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MTI Motion</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Pleasant Prairie, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Azure, Oracle, SQL Server, ELT, dbt, Power BI, Tableau, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f6c2033564fadc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Volantsoft Inc</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01c19f449674df9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, Power BI, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73bbf40e88ece05</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Data Engineering</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9959e16e7931f96e</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Java/Spring Boot/Kafka</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=704df45d73edd23e</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Java AWS Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a2deb552df5368e</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>nextPoint</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Software Engineer I- Enterprise AI Products</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=287e2617edce5555</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ferguson</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Newport News, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Databricks Lakehouse, Power BI, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior ML Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Advanced Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=813f3f55e6f0904d</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Developer DBA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Aeroflow Health</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Asheville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ad833078dc9770</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Nakupuna Companies</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, ETL, Power BI, Tableau, Azure DevOps, AKS</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=302f426881732dba</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Software Engineer (Full Stack Developer) - Remote</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ee89c82aaaecc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90dd2e7c995cb4c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Data Engineer L4 (Remote)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Frontdoor</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
         <v>10.4</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Datadog</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44dbc0a1e62ab6b6</t>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a9b135a0413894f</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07de84eaf7866caf</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Software Engineer III-ETL/PySpark</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea273207167a8ae8</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44f0c4a1bfd9338a</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Full Stack Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Custom Health</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, MySQL, MongoDB, DynamoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dca5d2f6227a7f3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>P17 Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Egg Harbor Township, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>S3, IAM, RDS, Oracle, PostgreSQL, CI/CD, Maven, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f241d5d943c65e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, Oracle, PostgreSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47d37c2372a4bc58</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Database Developer (SQL &amp; Databricks)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Rooms To Go</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Seffner, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Databricks Lakehouse, SQL Server, PostgreSQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7291666cf90be22a</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Splunk, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bccda3473d5c3eec</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Software Engineer Professional, Financial Engineering</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Freddie Mac</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, Jenkins, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af8a3a5fe3ef71bb</t>
         </is>
       </c>
     </row>
